--- a/data/availability/projects/ilcazar/vea-new-cairo.xlsx
+++ b/data/availability/projects/ilcazar/vea-new-cairo.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vea New Cairo latest availability</t>
+          <t>Updated inventory for vea-new-cairo</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -582,17 +582,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Vea District 6</t>
+          <t>District 6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 3 years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vea District 6</t>
+          <t>District 6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2 years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -735,17 +735,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VEA-TH-180</t>
+          <t>VEA-TH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vea District 6</t>
+          <t>District 6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -759,23 +759,27 @@
       <c r="G2" t="n">
         <v>180</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>180 SQM Townhouse</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>18227344</v>
+        <v>18227343</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 3 years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -797,12 +801,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VEA-SA-220</t>
+          <t>VEA-SA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vea District 6</t>
+          <t>District 6</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -816,10 +820,14 @@
       <c r="G3" t="n">
         <v>220</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>220 SQM Standalone C</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -827,12 +835,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2 years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
